--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121436350</v>
+        <v>121436576</v>
       </c>
       <c r="B2" t="n">
         <v>78601</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519408</v>
+        <v>519410</v>
       </c>
       <c r="R2" t="n">
-        <v>6995594</v>
+        <v>6995582</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121436576</v>
+        <v>121436350</v>
       </c>
       <c r="B3" t="n">
         <v>78601</v>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519410</v>
+        <v>519408</v>
       </c>
       <c r="R3" t="n">
-        <v>6995582</v>
+        <v>6995594</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121436576</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121436350</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121436576</v>
+        <v>121436350</v>
       </c>
       <c r="B2" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519410</v>
+        <v>519408</v>
       </c>
       <c r="R2" t="n">
-        <v>6995582</v>
+        <v>6995594</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121436350</v>
+        <v>121436576</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519408</v>
+        <v>519410</v>
       </c>
       <c r="R3" t="n">
-        <v>6995594</v>
+        <v>6995582</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121436350</v>
+        <v>121436576</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519408</v>
+        <v>519410</v>
       </c>
       <c r="R2" t="n">
-        <v>6995594</v>
+        <v>6995582</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121436576</v>
+        <v>121436350</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519410</v>
+        <v>519408</v>
       </c>
       <c r="R3" t="n">
-        <v>6995582</v>
+        <v>6995594</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121436576</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121436350</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121436576</v>
+        <v>121436350</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519410</v>
+        <v>519408</v>
       </c>
       <c r="R2" t="n">
-        <v>6995582</v>
+        <v>6995594</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121436350</v>
+        <v>121436576</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519408</v>
+        <v>519410</v>
       </c>
       <c r="R3" t="n">
-        <v>6995594</v>
+        <v>6995582</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121436350</v>
+        <v>121436576</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519408</v>
+        <v>519410</v>
       </c>
       <c r="R2" t="n">
-        <v>6995594</v>
+        <v>6995582</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121436576</v>
+        <v>121436350</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519410</v>
+        <v>519408</v>
       </c>
       <c r="R3" t="n">
-        <v>6995582</v>
+        <v>6995594</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121436576</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121436350</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,138 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129848060</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lorthålet, Lorthålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>519248</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6995501</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ella Hambeson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ella Hambeson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129848060</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129848060</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129848060</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129848060</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129848060</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129848060</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>121436350</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -790,16 +785,11 @@
         <v>121436576</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -902,11 +892,11 @@
         <v>129848060</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">

--- a/artfynd/A 22101-2024 artfynd.xlsx
+++ b/artfynd/A 22101-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -804,6 +809,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129848060</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121436350</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,8 +1033,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121436576</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>